--- a/benchmark/generated_files/CC-3_V_033.xlsx
+++ b/benchmark/generated_files/CC-3_V_033.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A2:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -443,31 +443,24 @@
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Saldo iniziale: 1.031,48 EUR</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codice cliente: 659606</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>Divisa: EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Periodo: 01/01/2026 - 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Tipo conto: Conto corrente</t>
         </is>
       </c>
     </row>
@@ -481,14 +474,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Movimenti al 28/02/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Tipo conto: Conto corrente</t>
+          <t>Saldo iniziale: 24.913,00 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Codice cliente: 242545</t>
         </is>
       </c>
     </row>
@@ -524,7 +517,7 @@
         <v>46023</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -532,7 +525,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1160.88</v>
+        <v>1209.96</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -545,7 +538,7 @@
         <v>46023</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -553,7 +546,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1168.52</v>
+        <v>1201.06</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -566,7 +559,7 @@
         <v>46023</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -574,7 +567,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1239.41</v>
+        <v>1180.69</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -595,7 +588,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1150.32</v>
+        <v>1184.15</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -616,7 +609,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1227.79</v>
+        <v>1236.03</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -637,7 +630,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1155.66</v>
+        <v>1164.46</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -658,7 +651,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1184.87</v>
+        <v>1189.47</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -679,7 +672,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1152.11</v>
+        <v>1189.78</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -692,7 +685,7 @@
         <v>46023</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -700,7 +693,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1233.12</v>
+        <v>1238.98</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -721,7 +714,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1204.24</v>
+        <v>1197.56</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -734,7 +727,7 @@
         <v>46023</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -742,7 +735,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1230.97</v>
+        <v>1182.69</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -755,7 +748,7 @@
         <v>46023</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -763,7 +756,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1171.68</v>
+        <v>1169.03</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -776,7 +769,7 @@
         <v>46023</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -784,7 +777,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1157.43</v>
+        <v>1246.69</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -805,7 +798,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1163.47</v>
+        <v>1190.1</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -826,7 +819,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1179.11</v>
+        <v>1195.19</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -847,7 +840,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1216.17</v>
+        <v>1192.27</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -868,7 +861,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1241.93</v>
+        <v>1216.58</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -889,7 +882,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1198.19</v>
+        <v>1201.83</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -902,7 +895,7 @@
         <v>46023</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -910,7 +903,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1188.68</v>
+        <v>1189.06</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -923,7 +916,7 @@
         <v>46023</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -931,7 +924,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1244.73</v>
+        <v>1159.04</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -941,18 +934,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:219451743 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1172.73</v>
+        <v>99.66</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -962,18 +955,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46023</v>
+        <v>46029</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>Pagam. POS - PAGAMENTO POS 168,45 EUR DEL 07.01.2026 A (ITA) IL GIGANTE FIRENZE</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1154.41</v>
+        <v>-168.45</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -983,18 +976,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46023</v>
+        <v>46030</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46023</v>
+        <v>46030</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:217902812 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1182.24</v>
+        <v>180.91</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1004,18 +997,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46023</v>
+        <v>46034</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46023</v>
+        <v>46034</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1150.54</v>
+        <v>-789.51</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1025,18 +1018,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46023</v>
+        <v>46034</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>Disposizione - RIF:215192858 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1202.95</v>
+        <v>-773.36</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1046,18 +1039,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46023</v>
+        <v>46035</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1229.84</v>
+        <v>-755.39</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1067,18 +1060,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46023</v>
+        <v>46036</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46023</v>
+        <v>46037</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:211550351 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1161.07</v>
+        <v>249.65</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1088,18 +1081,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46024</v>
+        <v>46039</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46024</v>
+        <v>46040</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 16,26 EUR DEL 02.01.2026 A (ITA) PARRUCCHIERA SONIA</t>
+          <t>Disposizione - RIF:218525928 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-16.26</v>
+        <v>-558.73</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1109,18 +1102,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46024</v>
+        <v>46040</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46024</v>
+        <v>46040</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+          <t>Disposizione - RIF:218297407 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-691.4</v>
+        <v>-647.76</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1130,18 +1123,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46026</v>
+        <v>46043</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46027</v>
+        <v>46043</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:215254291 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>Bonif. v/fav. - RIF:217078147 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-791.09</v>
+        <v>261.56</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1151,18 +1144,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46028</v>
+        <v>46047</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46029</v>
+        <v>46047</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210777145 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>415.68</v>
+        <v>-648.86</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1172,18 +1165,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46031</v>
+        <v>46048</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46032</v>
+        <v>46048</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+          <t>Bonif. v/fav. - RIF:210485316 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-470.43</v>
+        <v>447.32</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1193,18 +1186,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46032</v>
+        <v>46049</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46033</v>
+        <v>46050</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212982803 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4588 MERCATÒ LOCAL BARI</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>-733.1799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1214,18 +1207,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46035</v>
+        <v>46051</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46035</v>
+        <v>46051</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 01234 BANCO BPM</t>
+          <t>Pagam. POS - PAGAMENTO POS 5,39 EUR DEL 29.01.2026 A (ITA) IL PANE QUOTIDIANO BOLOGNA</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>-27.93</v>
+        <v>-5.39</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1235,18 +1228,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46038</v>
+        <v>46051</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46038</v>
+        <v>46052</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219401111 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6810 MERCATÒ VERONA</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>446.89</v>
+        <v>-21.91</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1256,18 +1249,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46039</v>
+        <v>46054</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46039</v>
+        <v>46054</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 3,26 EUR DEL 17.01.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>-3.26</v>
+        <v>1183.3</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1277,18 +1270,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46039</v>
+        <v>46054</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46039</v>
+        <v>46055</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 115,20 EUR DEL 17.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-115.2</v>
+        <v>1205.77</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1298,18 +1291,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46040</v>
+        <v>46054</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46041</v>
+        <v>46054</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216131631 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>220.88</v>
+        <v>1174.65</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1319,18 +1312,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46041</v>
+        <v>46054</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46041</v>
+        <v>46055</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 199,33 EUR DEL 19.01.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-199.33</v>
+        <v>1178.13</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -1340,18 +1333,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46046</v>
+        <v>46054</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210329169 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-863.55</v>
+        <v>1169.13</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -1361,18 +1354,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1981 LIDL ITALIA</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>-68.7</v>
+        <v>1221.99</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -1382,18 +1375,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>-677.9400000000001</v>
+        <v>1177.32</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -1406,7 +1399,7 @@
         <v>46054</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1407,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1235.68</v>
+        <v>1174.75</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -1427,7 +1420,7 @@
         <v>46054</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1428,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1190.2</v>
+        <v>1241.15</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1441,7 @@
         <v>46054</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -1456,7 +1449,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1243.35</v>
+        <v>1176.85</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1470,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1189.73</v>
+        <v>1239.76</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -1498,7 +1491,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1235.65</v>
+        <v>1229.55</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -1519,7 +1512,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1180.66</v>
+        <v>1163.52</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -1532,7 +1525,7 @@
         <v>46054</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1193.52</v>
+        <v>1155.96</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1546,7 @@
         <v>46054</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
@@ -1561,7 +1554,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1234.57</v>
+        <v>1162.54</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1567,7 @@
         <v>46054</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1575,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1228.51</v>
+        <v>1243.28</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -1603,7 +1596,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1249.6</v>
+        <v>1239.28</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -1624,7 +1617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1195.83</v>
+        <v>1175.59</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1645,7 +1638,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1163.07</v>
+        <v>1179.16</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -1658,7 +1651,7 @@
         <v>46054</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1659,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1234.15</v>
+        <v>1185.95</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -1679,7 +1672,7 @@
         <v>46054</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1680,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1163.96</v>
+        <v>1224.77</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -1700,7 +1693,7 @@
         <v>46054</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
@@ -1708,7 +1701,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1208.19</v>
+        <v>1176.46</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -1729,7 +1722,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1240.76</v>
+        <v>1224.32</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -1742,7 +1735,7 @@
         <v>46054</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
@@ -1750,7 +1743,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1238.66</v>
+        <v>1154.62</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1764,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1155.37</v>
+        <v>1229.79</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1777,7 @@
         <v>46054</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1785,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1211.74</v>
+        <v>1173.86</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -1813,7 +1806,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>1194.24</v>
+        <v>1197.89</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -1834,7 +1827,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1187.94</v>
+        <v>1158.55</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1840,7 @@
         <v>46054</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
@@ -1855,7 +1848,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1185.95</v>
+        <v>1219.41</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1869,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1231.13</v>
+        <v>1161.6</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -1889,7 +1882,7 @@
         <v>46054</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1890,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1242.65</v>
+        <v>1215.47</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -1918,7 +1911,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1232.87</v>
+        <v>1179.08</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -1939,7 +1932,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1187.6</v>
+        <v>1170.58</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -1952,7 +1945,7 @@
         <v>46054</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -1960,7 +1953,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1227.72</v>
+        <v>1164.45</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1966,7 @@
         <v>46054</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1974,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1235.03</v>
+        <v>1211.34</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -2002,7 +1995,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1226.58</v>
+        <v>1168.83</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -2015,7 +2008,7 @@
         <v>46054</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2016,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1156.28</v>
+        <v>1214.56</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2029,7 @@
         <v>46054</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
@@ -2044,7 +2037,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>1241.16</v>
+        <v>1224.28</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -2057,7 +2050,7 @@
         <v>46054</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2058,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>1230.81</v>
+        <v>1207.66</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2079,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1225.53</v>
+        <v>1213.4</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -2107,7 +2100,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1199.09</v>
+        <v>1174.86</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -2120,7 +2113,7 @@
         <v>46054</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2121,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1156.23</v>
+        <v>1222.43</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -2138,18 +2131,18 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46057</v>
+        <v>46054</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46057</v>
+        <v>46054</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 16,97 EUR DEL 04.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-16.97</v>
+        <v>1243.66</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -2159,18 +2152,18 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46058</v>
+        <v>46055</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217942323 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>171.09</v>
+        <v>-97.02</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -2180,18 +2173,18 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219637378 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>496.6</v>
+        <v>-960.01</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -2201,18 +2194,18 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212657234 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Pagam. POS - PAGAMENTO POS 8,10 EUR DEL 08.02.2026 A (ITA) COOP.FI VENEZIA</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>141.96</v>
+        <v>-8.1</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -2229,11 +2222,11 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216897388 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>386.71</v>
+        <v>-429.6</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -2243,18 +2236,18 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 66,74 EUR DEL 13.02.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 197,64 EUR DEL 09.02.2026 A (ITA) FIELMANN</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-66.73999999999999</v>
+        <v>-197.64</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -2264,18 +2257,18 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46068</v>
+        <v>46062</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46068</v>
+        <v>46063</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218559743 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Bonif. v/fav. - RIF:218427235 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>257.62</v>
+        <v>61.67</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -2285,18 +2278,18 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46070</v>
+        <v>46062</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46070</v>
+        <v>46063</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219599496 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>159.09</v>
+        <v>-400.43</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -2306,18 +2299,18 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46071</v>
+        <v>46063</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46071</v>
+        <v>46065</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219605637 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Pagam. POS - PAGAMENTO POS 108,51 EUR DEL 10.02.2026 A (ITA) IL GIGANTE MESTRE</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>-108.51</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -2327,18 +2320,18 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46076</v>
+        <v>46072</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 197,78 EUR DEL 21.02.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 139,58 EUR DEL 18.02.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>-197.78</v>
+        <v>-139.58</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -2348,18 +2341,18 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46077</v>
+        <v>46071</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46078</v>
+        <v>46072</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210097573 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>Bonif. v/fav. - RIF:210167970 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-968.26</v>
+        <v>138.96</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -2369,18 +2362,18 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210853853 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>Bonif. v/fav. - RIF:210039673 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>-828.27</v>
+        <v>152.16</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -2390,18 +2383,18 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:218989514 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>Bonif. v/fav. - RIF:218466348 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-872.0599999999999</v>
+        <v>377.46</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -2412,7 +2405,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Saldo finale: 14.374,16 EUR</t>
+          <t>Saldo finale: 15.005,04 EUR</t>
         </is>
       </c>
     </row>
